--- a/scripts/experementals/generic_tokens_expanded.xlsx
+++ b/scripts/experementals/generic_tokens_expanded.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rictus\IdeaProjects\tolstoy-words-local\scripts\experementals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D35626-E5AD-465E-A326-73FFD9BAD1B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA673C2C-9E37-4DD8-87BB-C54A1CC756CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2925" yWindow="2580" windowWidth="25815" windowHeight="11580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
   <si>
     <t>TokenID</t>
   </si>
@@ -86,6 +86,9 @@
   </si>
   <si>
     <t>VERB_HEAD</t>
+  </si>
+  <si>
+    <t>None</t>
   </si>
   <si>
     <t>запах</t>
@@ -556,19 +559,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" customWidth="1"/>
-    <col min="5" max="5" width="24.85546875" customWidth="1"/>
-    <col min="6" max="6" width="19.5703125" customWidth="1"/>
-    <col min="7" max="7" width="21" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -635,16 +632,19 @@
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2">
         <v>2331</v>
@@ -704,15 +704,15 @@
         <v>234</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3">
         <v>1783</v>
@@ -769,15 +769,15 @@
         <v>193</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>1115</v>
@@ -831,15 +831,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5">
         <v>905</v>
@@ -881,15 +881,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6">
         <v>913</v>
@@ -946,15 +946,15 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7">
         <v>819</v>
@@ -1011,15 +1011,15 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8">
         <v>642</v>
@@ -1073,15 +1073,15 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9">
         <v>394</v>
@@ -1135,15 +1135,15 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10">
         <v>367</v>
@@ -1200,15 +1200,15 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11">
         <v>192</v>
@@ -1256,15 +1256,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D12">
         <v>48</v>
@@ -1300,15 +1300,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13">
         <v>44</v>
@@ -1353,15 +1353,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D14">
         <v>18</v>
@@ -1388,15 +1388,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15">
         <v>12</v>
@@ -1423,15 +1423,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16">
         <v>8</v>
@@ -1464,15 +1464,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -1502,15 +1502,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1531,15 +1531,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" t="s">
         <v>56</v>
-      </c>
-      <c r="C19" t="s">
-        <v>55</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -1553,16 +1553,19 @@
       <c r="G19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D20">
         <v>1</v>

--- a/scripts/experementals/generic_tokens_expanded.xlsx
+++ b/scripts/experementals/generic_tokens_expanded.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rictus\IdeaProjects\tolstoy-words-local\scripts\experementals\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\PycharmProjects\tolstoy-words-local\scripts\experementals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA673C2C-9E37-4DD8-87BB-C54A1CC756CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -202,7 +201,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -558,11 +557,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:W20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" customWidth="1"/>
     <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">

--- a/scripts/experementals/generic_tokens_expanded.xlsx
+++ b/scripts/experementals/generic_tokens_expanded.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\PycharmProjects\tolstoy-words-local\scripts\experementals\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rictus\IdeaProjects\tolstoy-words-local\scripts\experementals\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C456CA68-82AC-4E4F-A4EA-AF14EE651143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10248"/>
+    <workbookView xWindow="2925" yWindow="2580" windowWidth="25815" windowHeight="11580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="78">
   <si>
     <t>TokenID</t>
   </si>
@@ -150,18 +151,6 @@
     <t>199</t>
   </si>
   <si>
-    <t>зловонный</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>пот</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>разить</t>
   </si>
   <si>
@@ -174,6 +163,12 @@
     <t>48</t>
   </si>
   <si>
+    <t>букет</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
     <t>веять</t>
   </si>
   <si>
@@ -186,109 +181,76 @@
     <t>12</t>
   </si>
   <si>
-    <t>душистый</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>ароматный</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>обоняние</t>
+    <t>дуновение</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>дуновение</t>
-  </si>
-  <si>
-    <t>нюхать</t>
+    <t>пахнуть</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>пахнуть</t>
+    <t>миазмы</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>навоз</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>амбра</t>
   </si>
   <si>
-    <t>миазмы</t>
+    <t>душок</t>
   </si>
   <si>
     <t>амбре</t>
   </si>
   <si>
-    <t>душок</t>
-  </si>
-  <si>
-    <t>потный</t>
+    <t>тухлятина</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
+    <t>фимиам</t>
+  </si>
+  <si>
     <t>чадить</t>
   </si>
   <si>
-    <t>фимиам</t>
-  </si>
-  <si>
-    <t>тухлятина</t>
-  </si>
-  <si>
-    <t>вонючий</t>
-  </si>
-  <si>
     <t>смердеть</t>
   </si>
   <si>
     <t>скверна</t>
   </si>
   <si>
+    <t>испарение</t>
+  </si>
+  <si>
+    <t>пригарь</t>
+  </si>
+  <si>
+    <t>попахивать</t>
+  </si>
+  <si>
+    <t>перегар</t>
+  </si>
+  <si>
+    <t>парфюм</t>
+  </si>
+  <si>
+    <t>одеколон</t>
+  </si>
+  <si>
+    <t>дерьмо</t>
+  </si>
+  <si>
     <t>вонять</t>
-  </si>
-  <si>
-    <t>пригарь</t>
-  </si>
-  <si>
-    <t>потеть</t>
-  </si>
-  <si>
-    <t>испарение</t>
-  </si>
-  <si>
-    <t>дерьмо</t>
-  </si>
-  <si>
-    <t>попахивать</t>
-  </si>
-  <si>
-    <t>перегар</t>
-  </si>
-  <si>
-    <t>пахучий</t>
-  </si>
-  <si>
-    <t>парфюм</t>
-  </si>
-  <si>
-    <t>одеколон</t>
-  </si>
-  <si>
-    <t>обонять</t>
   </si>
   <si>
     <t>чадо</t>
@@ -297,7 +259,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -653,16 +615,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W47"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:W37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.62890625" customWidth="1"/>
-    <col min="3" max="3" width="20.578125" customWidth="1"/>
-    <col min="5" max="5" width="10.26171875" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" customWidth="1"/>
+    <col min="3" max="3" width="28.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -733,7 +694,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -744,13 +705,13 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>2338</v>
+        <v>2331</v>
       </c>
       <c r="E2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="F2">
-        <v>15.85</v>
+        <v>15.93</v>
       </c>
       <c r="G2">
         <v>15</v>
@@ -762,7 +723,7 @@
         <v>21</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2">
         <v>2</v>
@@ -774,7 +735,7 @@
         <v>12</v>
       </c>
       <c r="N2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O2">
         <v>1</v>
@@ -795,13 +756,13 @@
         <v>5</v>
       </c>
       <c r="U2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="V2">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -815,16 +776,16 @@
         <v>1783</v>
       </c>
       <c r="E3">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="F3">
-        <v>16.100000000000001</v>
+        <v>16.05</v>
       </c>
       <c r="G3">
         <v>15</v>
       </c>
       <c r="H3">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I3">
         <v>17</v>
@@ -842,7 +803,7 @@
         <v>8</v>
       </c>
       <c r="N3">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="P3">
         <v>9</v>
@@ -863,10 +824,10 @@
         <v>91</v>
       </c>
       <c r="V3">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -880,55 +841,58 @@
         <v>1115</v>
       </c>
       <c r="E4">
-        <v>122</v>
+        <v>448</v>
       </c>
       <c r="F4">
-        <v>17.04</v>
+        <v>16.04</v>
       </c>
       <c r="G4">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N4">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S4">
         <v>1</v>
       </c>
+      <c r="T4">
+        <v>4</v>
+      </c>
       <c r="U4">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="V4">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -942,31 +906,55 @@
         <v>905</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>177</v>
       </c>
       <c r="F5">
-        <v>15.17</v>
+        <v>15.32</v>
       </c>
       <c r="G5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>25</v>
+      </c>
+      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>25</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>2</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
       </c>
       <c r="T5">
         <v>1</v>
       </c>
       <c r="U5">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="V5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -980,22 +968,22 @@
         <v>913</v>
       </c>
       <c r="E6">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="F6">
-        <v>15.53</v>
+        <v>15.38</v>
       </c>
       <c r="G6">
         <v>15</v>
       </c>
       <c r="H6">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -1007,10 +995,10 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6">
         <v>3</v>
@@ -1025,13 +1013,13 @@
         <v>1</v>
       </c>
       <c r="U6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="V6">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1045,19 +1033,19 @@
         <v>819</v>
       </c>
       <c r="E7">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="F7">
-        <v>16.86</v>
+        <v>16.71</v>
       </c>
       <c r="G7">
         <v>16</v>
       </c>
       <c r="H7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1072,7 +1060,7 @@
         <v>4</v>
       </c>
       <c r="N7">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="P7">
         <v>3</v>
@@ -1090,13 +1078,13 @@
         <v>1</v>
       </c>
       <c r="U7">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="V7">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1110,10 +1098,10 @@
         <v>642</v>
       </c>
       <c r="E8">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="F8">
-        <v>15.88</v>
+        <v>15.68</v>
       </c>
       <c r="G8">
         <v>15</v>
@@ -1122,7 +1110,7 @@
         <v>16</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>5</v>
@@ -1137,7 +1125,7 @@
         <v>4</v>
       </c>
       <c r="N8">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="P8">
         <v>6</v>
@@ -1152,13 +1140,13 @@
         <v>2</v>
       </c>
       <c r="U8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="V8">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1175,7 +1163,7 @@
         <v>221</v>
       </c>
       <c r="F9">
-        <v>15.34</v>
+        <v>15.18</v>
       </c>
       <c r="G9">
         <v>15</v>
@@ -1220,7 +1208,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1234,37 +1222,37 @@
         <v>367</v>
       </c>
       <c r="E10">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="F10">
-        <v>17.510000000000002</v>
+        <v>16.510000000000002</v>
       </c>
       <c r="G10">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H10">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10">
         <v>2</v>
       </c>
       <c r="M10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N10">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="P10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q10">
         <v>2</v>
@@ -1276,16 +1264,16 @@
         <v>1</v>
       </c>
       <c r="T10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U10">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="V10">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1299,32 +1287,32 @@
         <v>192</v>
       </c>
       <c r="E11">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F11">
-        <v>15.44</v>
+        <v>15.31</v>
       </c>
       <c r="G11">
         <v>15</v>
       </c>
       <c r="H11">
+        <v>12</v>
+      </c>
+      <c r="I11">
+        <v>4</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>2</v>
+      </c>
+      <c r="N11">
         <v>10</v>
       </c>
-      <c r="I11">
-        <v>3</v>
-      </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <v>2</v>
-      </c>
-      <c r="N11">
-        <v>9</v>
-      </c>
       <c r="P11">
         <v>1</v>
       </c>
@@ -1335,13 +1323,13 @@
         <v>1</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1352,25 +1340,49 @@
         <v>44</v>
       </c>
       <c r="D12">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="F12">
+        <v>18.43</v>
+      </c>
+      <c r="G12">
+        <v>17</v>
+      </c>
+      <c r="I12">
+        <v>3</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>4</v>
+      </c>
+      <c r="N12">
+        <v>7</v>
+      </c>
+      <c r="P12">
+        <v>2</v>
+      </c>
+      <c r="Q12">
+        <v>2</v>
+      </c>
+      <c r="U12">
+        <v>3</v>
+      </c>
+      <c r="V12">
         <v>16</v>
       </c>
-      <c r="G12">
-        <v>14</v>
-      </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-      <c r="P12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1381,25 +1393,40 @@
         <v>46</v>
       </c>
       <c r="D13">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="F13">
-        <v>17</v>
+        <v>19.2</v>
       </c>
       <c r="G13">
-        <v>14</v>
+        <v>19</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>4</v>
       </c>
       <c r="L13">
         <v>1</v>
       </c>
       <c r="N13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+        <v>10</v>
+      </c>
+      <c r="Q13">
+        <v>2</v>
+      </c>
+      <c r="U13">
+        <v>2</v>
+      </c>
+      <c r="V13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1410,22 +1437,49 @@
         <v>48</v>
       </c>
       <c r="D14">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>16.02</v>
       </c>
       <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+        <v>15</v>
+      </c>
+      <c r="H14">
+        <v>15</v>
+      </c>
+      <c r="I14">
+        <v>4</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>9</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>2</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>7</v>
+      </c>
+      <c r="V14">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1436,22 +1490,37 @@
         <v>50</v>
       </c>
       <c r="D15">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>14.89</v>
       </c>
       <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+        <v>15</v>
+      </c>
+      <c r="J15">
+        <v>3</v>
+      </c>
+      <c r="N15">
+        <v>13</v>
+      </c>
+      <c r="Q15">
+        <v>4</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>3</v>
+      </c>
+      <c r="V15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1462,22 +1531,31 @@
         <v>52</v>
       </c>
       <c r="D16">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+        <v>13</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>3</v>
+      </c>
+      <c r="U16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1488,16 +1566,19 @@
         <v>54</v>
       </c>
       <c r="D17">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F17">
+        <v>16</v>
+      </c>
+      <c r="G17">
         <v>14</v>
       </c>
-      <c r="G17">
-        <v>13</v>
+      <c r="H17">
+        <v>2</v>
       </c>
       <c r="I17">
         <v>1</v>
@@ -1506,13 +1587,16 @@
         <v>1</v>
       </c>
       <c r="N17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1523,22 +1607,40 @@
         <v>56</v>
       </c>
       <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18">
         <v>10</v>
       </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
       <c r="F18">
-        <v>17.329999999999998</v>
+        <v>14.67</v>
       </c>
       <c r="G18">
-        <v>18</v>
+        <v>14</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
       </c>
       <c r="L18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="N18">
+        <v>3</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1549,22 +1651,25 @@
         <v>58</v>
       </c>
       <c r="D19">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="W19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+        <v>22</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="V19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1572,112 +1677,97 @@
         <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D20">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>17</v>
-      </c>
-      <c r="I20">
-        <v>2</v>
-      </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
-      <c r="P20">
-        <v>2</v>
-      </c>
-      <c r="V20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F21">
-        <v>15.43</v>
+        <v>20</v>
       </c>
       <c r="G21">
-        <v>14</v>
-      </c>
-      <c r="H21">
-        <v>2</v>
-      </c>
-      <c r="I21">
-        <v>1</v>
-      </c>
-      <c r="N21">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="U21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V21">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C22" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+        <v>16</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="V22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F23">
         <v>20</v>
@@ -1685,34 +1775,25 @@
       <c r="G23">
         <v>20</v>
       </c>
-      <c r="J23">
-        <v>1</v>
-      </c>
-      <c r="K23">
-        <v>1</v>
-      </c>
-      <c r="N23">
-        <v>1</v>
-      </c>
       <c r="U23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V23">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1727,18 +1808,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1753,76 +1834,70 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>22</v>
-      </c>
-      <c r="M26">
-        <v>1</v>
-      </c>
-      <c r="V26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>20</v>
-      </c>
-      <c r="U27">
-        <v>2</v>
-      </c>
-      <c r="V27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1837,15 +1912,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1863,15 +1938,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1889,15 +1964,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1915,15 +1990,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1941,15 +2016,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C33" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -1967,15 +2042,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1993,15 +2068,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C35" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -2019,15 +2094,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C36" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -2045,15 +2120,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C37" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -2068,266 +2143,6 @@
         <v>0</v>
       </c>
       <c r="W37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
-        <v>81</v>
-      </c>
-      <c r="C38" t="s">
-        <v>72</v>
-      </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38">
-        <v>0</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="W38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="s">
-        <v>82</v>
-      </c>
-      <c r="C39" t="s">
-        <v>72</v>
-      </c>
-      <c r="D39">
-        <v>0</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="W39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="s">
-        <v>83</v>
-      </c>
-      <c r="C40" t="s">
-        <v>72</v>
-      </c>
-      <c r="D40">
-        <v>0</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="W40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="s">
-        <v>84</v>
-      </c>
-      <c r="C41" t="s">
-        <v>72</v>
-      </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="W41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="s">
-        <v>85</v>
-      </c>
-      <c r="C42" t="s">
-        <v>72</v>
-      </c>
-      <c r="D42">
-        <v>0</v>
-      </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
-      <c r="F42">
-        <v>0</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="W42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="s">
-        <v>86</v>
-      </c>
-      <c r="C43" t="s">
-        <v>72</v>
-      </c>
-      <c r="D43">
-        <v>0</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="W43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="s">
-        <v>87</v>
-      </c>
-      <c r="C44" t="s">
-        <v>72</v>
-      </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
-      <c r="E44">
-        <v>0</v>
-      </c>
-      <c r="F44">
-        <v>0</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="W44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C45" t="s">
-        <v>72</v>
-      </c>
-      <c r="D45">
-        <v>0</v>
-      </c>
-      <c r="E45">
-        <v>0</v>
-      </c>
-      <c r="F45">
-        <v>0</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="W45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="s">
-        <v>89</v>
-      </c>
-      <c r="C46" t="s">
-        <v>72</v>
-      </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-      <c r="F46">
-        <v>0</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="W46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="s">
-        <v>90</v>
-      </c>
-      <c r="C47" t="s">
-        <v>72</v>
-      </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
-      <c r="F47">
-        <v>0</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="W47">
         <v>0</v>
       </c>
     </row>

--- a/scripts/experementals/generic_tokens_expanded.xlsx
+++ b/scripts/experementals/generic_tokens_expanded.xlsx
@@ -563,7 +563,7 @@
         <v>2330</v>
       </c>
       <c r="E2" t="n">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F2" t="n">
         <v>15.93</v>
@@ -590,7 +590,7 @@
         <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -614,7 +614,7 @@
         <v>102</v>
       </c>
       <c r="V2" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="W2" t="inlineStr"/>
     </row>
@@ -1058,54 +1058,56 @@
         <v>141</v>
       </c>
       <c r="E9" t="n">
-        <v>123</v>
+        <v>448</v>
       </c>
       <c r="F9" t="n">
-        <v>16.99</v>
+        <v>16.04</v>
       </c>
       <c r="G9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>40</v>
+        <v>119</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" t="inlineStr"/>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
       <c r="U9" t="n">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="V9" t="n">
-        <v>38</v>
+        <v>170</v>
       </c>
       <c r="W9" t="inlineStr"/>
     </row>
@@ -1127,19 +1129,19 @@
         <v>132</v>
       </c>
       <c r="E10" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F10" t="n">
-        <v>15.24</v>
+        <v>15.31</v>
       </c>
       <c r="G10" t="n">
         <v>15</v>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
@@ -1152,7 +1154,7 @@
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
@@ -1167,10 +1169,10 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W10" t="inlineStr"/>
     </row>
@@ -1255,35 +1257,43 @@
         <v>24</v>
       </c>
       <c r="E12" t="n">
-        <v>39</v>
+        <v>177</v>
       </c>
       <c r="F12" t="n">
-        <v>16.48</v>
+        <v>15.32</v>
       </c>
       <c r="G12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
       <c r="N12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
       <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
@@ -1291,10 +1301,10 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="V12" t="n">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="W12" t="inlineStr"/>
     </row>
@@ -1316,44 +1326,42 @@
         <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>16.53</v>
+        <v>14.67</v>
       </c>
       <c r="G13" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W13" t="inlineStr"/>
     </row>
@@ -1679,36 +1687,40 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F20" t="n">
-        <v>15</v>
+        <v>14.89</v>
       </c>
       <c r="G20" t="n">
         <v>15</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="n">
         <v>1</v>
       </c>
-      <c r="U20" t="inlineStr"/>
+      <c r="U20" t="n">
+        <v>3</v>
+      </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W20" t="inlineStr"/>
     </row>
@@ -2045,32 +2057,50 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>18.43</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>4</v>
+      </c>
+      <c r="N28" t="n">
+        <v>7</v>
+      </c>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2</v>
+      </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
+      <c r="U28" t="n">
+        <v>3</v>
+      </c>
+      <c r="V28" t="n">
+        <v>16</v>
+      </c>
+      <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2315,16 +2345,18 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -2337,10 +2369,10 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">

--- a/scripts/experementals/generic_tokens_expanded.xlsx
+++ b/scripts/experementals/generic_tokens_expanded.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W37"/>
+  <dimension ref="A1:W89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,65 +556,65 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2330</v>
+        <v>5029</v>
       </c>
       <c r="E2" t="n">
-        <v>654</v>
+        <v>1306</v>
       </c>
       <c r="F2" t="n">
-        <v>15.93</v>
+        <v>15.46</v>
       </c>
       <c r="G2" t="n">
         <v>15</v>
       </c>
       <c r="H2" t="n">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="I2" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="J2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="N2" t="n">
-        <v>175</v>
+        <v>348</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Q2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U2" t="n">
-        <v>102</v>
+        <v>203</v>
       </c>
       <c r="V2" t="n">
-        <v>235</v>
+        <v>473</v>
       </c>
       <c r="W2" t="inlineStr"/>
     </row>
@@ -629,63 +629,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1768</v>
+        <v>4077</v>
       </c>
       <c r="E3" t="n">
-        <v>552</v>
+        <v>1111</v>
       </c>
       <c r="F3" t="n">
-        <v>16.05</v>
+        <v>15.79</v>
       </c>
       <c r="G3" t="n">
         <v>15</v>
       </c>
       <c r="H3" t="n">
-        <v>74</v>
+        <v>152</v>
       </c>
       <c r="I3" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N3" t="n">
-        <v>134</v>
+        <v>265</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U3" t="n">
-        <v>91</v>
+        <v>182</v>
       </c>
       <c r="V3" t="n">
-        <v>195</v>
+        <v>392</v>
       </c>
       <c r="W3" t="inlineStr"/>
     </row>
@@ -700,63 +700,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>913</v>
+        <v>1976</v>
       </c>
       <c r="E4" t="n">
-        <v>300</v>
+        <v>602</v>
       </c>
       <c r="F4" t="n">
-        <v>15.38</v>
+        <v>15.21</v>
       </c>
       <c r="G4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H4" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N4" t="n">
-        <v>67</v>
+        <v>136</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="V4" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="W4" t="inlineStr"/>
     </row>
@@ -771,63 +771,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>819</v>
+        <v>1664</v>
       </c>
       <c r="E5" t="n">
-        <v>254</v>
+        <v>517</v>
       </c>
       <c r="F5" t="n">
-        <v>16.71</v>
+        <v>16.66</v>
       </c>
       <c r="G5" t="n">
         <v>16</v>
       </c>
       <c r="H5" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N5" t="n">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="V5" t="n">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="W5" t="inlineStr"/>
     </row>
@@ -842,61 +842,61 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>642</v>
+        <v>1293</v>
       </c>
       <c r="E6" t="n">
-        <v>266</v>
+        <v>534</v>
       </c>
       <c r="F6" t="n">
-        <v>15.68</v>
+        <v>15.62</v>
       </c>
       <c r="G6" t="n">
         <v>15</v>
       </c>
       <c r="H6" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="I6" t="n">
+        <v>20</v>
+      </c>
+      <c r="J6" t="n">
         <v>10</v>
       </c>
-      <c r="J6" t="n">
-        <v>5</v>
-      </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="V6" t="n">
-        <v>110</v>
+        <v>222</v>
       </c>
       <c r="W6" t="inlineStr"/>
     </row>
@@ -911,61 +911,61 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>796</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>394</v>
+        <v>796</v>
       </c>
       <c r="E7" t="n">
-        <v>221</v>
+        <v>448</v>
       </c>
       <c r="F7" t="n">
-        <v>15.18</v>
+        <v>15.15</v>
       </c>
       <c r="G7" t="n">
         <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N7" t="n">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U7" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="V7" t="n">
-        <v>99</v>
+        <v>198</v>
       </c>
       <c r="W7" t="inlineStr"/>
     </row>
@@ -980,63 +980,63 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>772</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>367</v>
+        <v>770</v>
       </c>
       <c r="E8" t="n">
-        <v>220</v>
+        <v>442</v>
       </c>
       <c r="F8" t="n">
-        <v>16.51</v>
+        <v>16.16</v>
       </c>
       <c r="G8" t="n">
         <v>15</v>
       </c>
       <c r="H8" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="I8" t="n">
+        <v>14</v>
+      </c>
+      <c r="J8" t="n">
         <v>7</v>
       </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N8" t="n">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="V8" t="n">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="W8" t="inlineStr"/>
     </row>
@@ -1051,45 +1051,45 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>286</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>141</v>
+        <v>286</v>
       </c>
       <c r="E9" t="n">
-        <v>448</v>
+        <v>255</v>
       </c>
       <c r="F9" t="n">
-        <v>16.04</v>
+        <v>16.93</v>
       </c>
       <c r="G9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
         <v>2</v>
@@ -1098,16 +1098,14 @@
         <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="n">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="V9" t="n">
-        <v>170</v>
+        <v>79</v>
       </c>
       <c r="W9" t="inlineStr"/>
     </row>
@@ -1122,57 +1120,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>271</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>132</v>
+        <v>271</v>
       </c>
       <c r="E10" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>15.31</v>
+        <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>15</v>
-      </c>
-      <c r="H10" t="n">
-        <v>12</v>
-      </c>
-      <c r="I10" t="n">
-        <v>4</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N10" t="n">
-        <v>10</v>
-      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>8</v>
-      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="W10" t="inlineStr"/>
     </row>
@@ -1182,61 +1160,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>букет</t>
+          <t>зловонный</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>230</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>44</v>
+        <v>228</v>
       </c>
       <c r="E11" t="n">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
-        <v>16.02</v>
+        <v>16.5</v>
       </c>
       <c r="G11" t="n">
-        <v>15</v>
-      </c>
-      <c r="H11" t="n">
-        <v>15</v>
-      </c>
-      <c r="I11" t="n">
-        <v>4</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>4</v>
+      </c>
       <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>9</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>7</v>
-      </c>
-      <c r="V11" t="n">
-        <v>25</v>
-      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1245,67 +1209,43 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>дух</t>
+          <t>затхлость</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>169</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>24</v>
+        <v>169</v>
       </c>
       <c r="E12" t="n">
-        <v>177</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>15.32</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>14</v>
-      </c>
-      <c r="H12" t="n">
-        <v>25</v>
-      </c>
-      <c r="I12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>14</v>
-      </c>
-      <c r="V12" t="n">
-        <v>96</v>
-      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1314,56 +1254,44 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>пахнуть</t>
+          <t>источать</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>14.67</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
-        <v>3</v>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" t="n">
-        <v>2</v>
-      </c>
-      <c r="W13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1371,49 +1299,61 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ладан</t>
+          <t>дух</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>17.02</v>
       </c>
       <c r="G14" t="n">
-        <v>13</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="H14" t="n">
+        <v>24</v>
+      </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4</v>
+      </c>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
       <c r="U14" t="n">
-        <v>3</v>
-      </c>
-      <c r="V14" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="V14" t="n">
+        <v>20</v>
+      </c>
       <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1422,40 +1362,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>дуновение</t>
+          <t>сандал</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E15" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G15" t="n">
-        <v>14</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -1463,12 +1397,8 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4</v>
-      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1477,56 +1407,44 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>благоухать</t>
+          <t>прелый</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="E16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>19</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
-        <v>4</v>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
-        <v>10</v>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="n">
-        <v>2</v>
-      </c>
-      <c r="V16" t="n">
-        <v>2</v>
-      </c>
-      <c r="W16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1534,44 +1452,62 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>миазмы</t>
+          <t>пахнуть</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>89</v>
       </c>
       <c r="F17" t="n">
-        <v>22</v>
+        <v>16.71</v>
       </c>
       <c r="G17" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>16</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>36</v>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+      <c r="Q17" t="n">
+        <v>5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>12</v>
+      </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W17" t="inlineStr"/>
     </row>
@@ -1581,33 +1517,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>амбре</t>
+          <t>ладан</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F18" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G18" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>8</v>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
@@ -1615,11 +1557,9 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="n">
-        <v>2</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1628,25 +1568,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>амбра</t>
+          <t>гарь</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -1661,13 +1601,11 @@
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1675,54 +1613,46 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>веять</t>
+          <t>душистый</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E20" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>14.89</v>
+        <v>15.37</v>
       </c>
       <c r="G20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
-        <v>3</v>
-      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
-        <v>13</v>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="n">
-        <v>4</v>
-      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3</v>
-      </c>
-      <c r="V20" t="n">
-        <v>3</v>
-      </c>
-      <c r="W20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1730,33 +1660,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>навоз</t>
+          <t>шлейф</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>2</v>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
@@ -1764,10 +1698,10 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
+      <c r="V21" t="n">
+        <v>2</v>
+      </c>
+      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1775,44 +1709,54 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>смердеть</t>
+          <t>обоняние</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>16.55</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>8</v>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2</v>
+      </c>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>4</v>
+      </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
+      <c r="V22" t="n">
+        <v>10</v>
+      </c>
+      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1820,25 +1764,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>скверна</t>
+          <t>ароматный</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -1848,7 +1792,9 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
@@ -1865,44 +1811,60 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>тухлятина</t>
+          <t>благоухать</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>19.09</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>8</v>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>2</v>
+      </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>22</v>
+      </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+      <c r="Q24" t="n">
+        <v>4</v>
+      </c>
       <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>6</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6</v>
+      </c>
+      <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1910,44 +1872,52 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>пригарь</t>
+          <t>благовонный</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2</v>
+      </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>2</v>
+      </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
+      <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1955,16 +1925,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>фимиам</t>
+          <t>ароматический</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -2000,31 +1970,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>чадить</t>
+          <t>мускус</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>2</v>
+      </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -2034,10 +2008,10 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
+      <c r="V27" t="n">
+        <v>2</v>
+      </c>
+      <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2045,61 +2019,45 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>разить</t>
+          <t>пот</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>18.43</v>
+        <v>16.75</v>
       </c>
       <c r="G28" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>4</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2</v>
-      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="n">
-        <v>3</v>
-      </c>
-      <c r="V28" t="n">
-        <v>16</v>
-      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -2108,31 +2066,37 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>испарение</t>
+          <t>амбре</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>2</v>
+      </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
@@ -2141,11 +2105,13 @@
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
+      <c r="U29" t="n">
+        <v>6</v>
+      </c>
+      <c r="V29" t="n">
+        <v>4</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2153,16 +2119,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>попахивать</t>
+          <t>обонятельный</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -2198,31 +2164,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>перегар</t>
+          <t>амбра</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2</v>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>2</v>
+      </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -2231,11 +2203,13 @@
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
+      <c r="U31" t="n">
+        <v>6</v>
+      </c>
+      <c r="V31" t="n">
+        <v>4</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2248,23 +2222,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -2276,7 +2252,9 @@
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" t="n">
+        <v>2</v>
+      </c>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="n">
         <v>0</v>
@@ -2288,31 +2266,33 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>одеколон</t>
+          <t>палёный</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>2</v>
+      </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -2323,9 +2303,7 @@
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
+      <c r="W33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2333,46 +2311,52 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>душок</t>
+          <t>тухлятина</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F34" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G34" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="n">
-        <v>1</v>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>2</v>
+      </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
+      <c r="Q34" t="n">
+        <v>4</v>
+      </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
+      <c r="U34" t="n">
+        <v>2</v>
+      </c>
       <c r="V34" t="n">
-        <v>1</v>
-      </c>
-      <c r="W34" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2380,25 +2364,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>дерьмо</t>
+          <t>веять</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -2406,18 +2390,26 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>6</v>
+      </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
+      <c r="Q35" t="n">
+        <v>2</v>
+      </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
+      </c>
+      <c r="V35" t="n">
+        <v>4</v>
+      </c>
+      <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2425,41 +2417,51 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>вонять</t>
+          <t>смердеть</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4</v>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>2</v>
+      </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>4</v>
+      </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="U36" t="n">
+        <v>2</v>
+      </c>
+      <c r="V36" t="n">
+        <v>2</v>
+      </c>
       <c r="W36" t="n">
         <v>0</v>
       </c>
@@ -2470,16 +2472,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>чадо</t>
+          <t>навоз</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -2509,6 +2511,2440 @@
         <v>0</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>дымить</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>8</v>
+      </c>
+      <c r="F38" t="n">
+        <v>35</v>
+      </c>
+      <c r="G38" t="n">
+        <v>35</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>2</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>2</v>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="n">
+        <v>2</v>
+      </c>
+      <c r="V38" t="n">
+        <v>2</v>
+      </c>
+      <c r="W38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>пропахнуть</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>10</v>
+      </c>
+      <c r="F39" t="n">
+        <v>35</v>
+      </c>
+      <c r="G39" t="n">
+        <v>35</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>4</v>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="n">
+        <v>2</v>
+      </c>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="n">
+        <v>2</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>перегар</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>16</v>
+      </c>
+      <c r="G40" t="n">
+        <v>16</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="n">
+        <v>2</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>попахивать</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>6</v>
+      </c>
+      <c r="F41" t="n">
+        <v>16</v>
+      </c>
+      <c r="G41" t="n">
+        <v>16</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>2</v>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>2</v>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="n">
+        <v>2</v>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>бальзамический</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>потеть</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" t="n">
+        <v>16</v>
+      </c>
+      <c r="G43" t="n">
+        <v>16</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>4</v>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="n">
+        <v>2</v>
+      </c>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>потный</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" t="n">
+        <v>16</v>
+      </c>
+      <c r="G44" t="n">
+        <v>16</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="n">
+        <v>2</v>
+      </c>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>пригарь</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" t="n">
+        <v>35</v>
+      </c>
+      <c r="G45" t="n">
+        <v>35</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="n">
+        <v>2</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>разить</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="n">
+        <v>10</v>
+      </c>
+      <c r="F46" t="n">
+        <v>16</v>
+      </c>
+      <c r="G46" t="n">
+        <v>16</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="n">
+        <v>2</v>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="n">
+        <v>2</v>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="n">
+        <v>2</v>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="n">
+        <v>2</v>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="n">
+        <v>2</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>благоуханный</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ароматизированный</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>скверна</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" t="n">
+        <v>22</v>
+      </c>
+      <c r="G49" t="n">
+        <v>22</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="n">
+        <v>2</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>амбровый</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>унюхивать</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" t="n">
+        <v>8</v>
+      </c>
+      <c r="F51" t="n">
+        <v>20</v>
+      </c>
+      <c r="G51" t="n">
+        <v>20</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="n">
+        <v>2</v>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="n">
+        <v>2</v>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="n">
+        <v>2</v>
+      </c>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="n">
+        <v>2</v>
+      </c>
+      <c r="W51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>фимиам</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" t="n">
+        <v>14</v>
+      </c>
+      <c r="G52" t="n">
+        <v>14</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="n">
+        <v>2</v>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>флера</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" t="n">
+        <v>20</v>
+      </c>
+      <c r="G53" t="n">
+        <v>20</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>чадить</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" t="n">
+        <v>14</v>
+      </c>
+      <c r="F54" t="n">
+        <v>35</v>
+      </c>
+      <c r="G54" t="n">
+        <v>35</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="n">
+        <v>4</v>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="n">
+        <v>2</v>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="n">
+        <v>4</v>
+      </c>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="n">
+        <v>2</v>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="n">
+        <v>2</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>чадо</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" t="n">
+        <v>6</v>
+      </c>
+      <c r="F55" t="n">
+        <v>35</v>
+      </c>
+      <c r="G55" t="n">
+        <v>35</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2</v>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="n">
+        <v>2</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>пахучий</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>нашатырь</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" t="n">
+        <v>6</v>
+      </c>
+      <c r="F57" t="n">
+        <v>21</v>
+      </c>
+      <c r="G57" t="n">
+        <v>21</v>
+      </c>
+      <c r="H57" t="n">
+        <v>2</v>
+      </c>
+      <c r="I57" t="n">
+        <v>2</v>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="n">
+        <v>2</v>
+      </c>
+      <c r="W57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>миазмы</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4</v>
+      </c>
+      <c r="F58" t="n">
+        <v>22</v>
+      </c>
+      <c r="G58" t="n">
+        <v>22</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="n">
+        <v>2</v>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="n">
+        <v>2</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>дегтярный</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2</v>
+      </c>
+      <c r="F59" t="n">
+        <v>20</v>
+      </c>
+      <c r="G59" t="n">
+        <v>20</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>отдушка</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" t="n">
+        <v>6</v>
+      </c>
+      <c r="F60" t="n">
+        <v>18</v>
+      </c>
+      <c r="G60" t="n">
+        <v>18</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="n">
+        <v>2</v>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>вонючий</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>кислятина</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>нюхать</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" t="n">
+        <v>8</v>
+      </c>
+      <c r="F63" t="n">
+        <v>20</v>
+      </c>
+      <c r="G63" t="n">
+        <v>20</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="n">
+        <v>4</v>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="n">
+        <v>4</v>
+      </c>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>гнилостный</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" t="n">
+        <v>4</v>
+      </c>
+      <c r="F64" t="n">
+        <v>15</v>
+      </c>
+      <c r="G64" t="n">
+        <v>15</v>
+      </c>
+      <c r="H64" t="n">
+        <v>2</v>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="n">
+        <v>2</v>
+      </c>
+      <c r="W64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>дерьмо</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2</v>
+      </c>
+      <c r="F65" t="n">
+        <v>20</v>
+      </c>
+      <c r="G65" t="n">
+        <v>20</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="n">
+        <v>2</v>
+      </c>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>одеколон</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2</v>
+      </c>
+      <c r="F66" t="n">
+        <v>22</v>
+      </c>
+      <c r="G66" t="n">
+        <v>22</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="n">
+        <v>2</v>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>вонять</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" t="n">
+        <v>6</v>
+      </c>
+      <c r="F67" t="n">
+        <v>25</v>
+      </c>
+      <c r="G67" t="n">
+        <v>25</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="n">
+        <v>4</v>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>зловонность</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>унюхать</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>душистость</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>испарение</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>спарение</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>смрадный</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>вспотеть</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>чуять</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>парфюмерный</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>смердение</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>разящий</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>вонючка</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>разита</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>пропотеть</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>нюх</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ароматизировать</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>почуять</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>вонючесть</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>обонять</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>душок</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>пованивать</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>понюхать</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
